--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
@@ -738,75 +738,285 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="5" t="n"/>
+    <row r="10" s="9">
+      <c r="B10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>CP-037 (navegación con sesión)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - encabezado</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Al presionar el logo de FitSearch con la sesión iniciada se abría el perfil en vez de un inicio.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Informado por el Product Owner el 02-10-2026. Corregido el 03-10-2026: el logo lleva al Inicio (/inicio) con sesión y a la portada (/) sin ella (FS-HU-21).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" s="9">
+      <c r="B11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>CP-042 (búsqueda de profesionales)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - encabezado</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>El encabezado tenía un elemento con apariencia de buscador ("Buscar profesionales") que en realidad era un enlace; confundía porque no permitía escribir.</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Interfaz</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Informado por el Product Owner el 02-10-2026. Corregido el 03-10-2026: primero se reemplazó por un enlace "Profesionales" y, por decisión del Product Owner, luego se quitó del encabezado, porque el menú lateral, la barra inferior y los accesos rápidos del Inicio ya llevan a Profesionales. La búsqueda real está en /profesionales (FS-HU-22).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" s="9">
+      <c r="B12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>CP-036 (portada pública)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - portada</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>La portada decía "Regístrate con tu correo y elige tu rol", pero desde el 24-09-2026 el tipo de cuenta se elige en el asistente de perfil (DAS, D21).</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 02-10-2026 al revisar el código para el rediseño. Corregido el 03-10-2026 en el paso 2 de "Cómo funciona".</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" s="9">
+      <c r="B13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>CP-043 (filtros del buscador)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Backend - profesionales</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>El filtro por comuna buscaba el texto en la dirección del establecimiento: los profesionales que atienden sin establecimiento nunca aparecían al filtrar por comuna.</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 02-10-2026 al revisar el modelo. Corregido el 03-10-2026 con la columna profesionales.comuna (migración 20261003120000_busqueda_profesionales).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" s="9">
+      <c r="B14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>CP-043 (revisión visual)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - estilos</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>En el entorno de desarrollo, index.css se carga después de los estilos de cada pantalla: el botón "Filtros" del celular se veía en escritorio, el corazón de favorito no quedaba en la esquina y el botón "Iniciar sesión" de la portada perdía su estilo.</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Interfaz</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 03-10-2026 al revisar las pantallas en el navegador. Las reglas que modifican .boton o .boton-icono usan ahora dos clases para no depender del orden de carga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" s="9">
+      <c r="B15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>CP-038 (registro y asistente)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - diseño común</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Después de registrarse, el aviso "Tu cuenta fue creada y la sesión está iniciada" seguía visible en todos los pasos del asistente de perfil.</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Interfaz</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 03-10-2026 al recorrer el asistente en el navegador. El aviso se descarta al guardar el primer paso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" s="9">
+      <c r="B16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>CP-038 (prueba automatizada del registro)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - navegación</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Una cuenta recién creada podía llegar primero al Inicio y luego saltar al asistente, perdiendo el aviso de cuenta creada.</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 03-10-2026 por la prueba automatizada del registro. La redirección de las pantallas de acceso usa el destino del aviso (/perfil) para las cuentas nuevas.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="3" t="n"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
@@ -392,7 +392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I1000"/>
+  <dimension ref="A1:I1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="9.380000000000001" customWidth="1" style="9" min="1" max="1"/>
@@ -1018,105 +1018,405 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" s="9">
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" s="9">
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" s="9">
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" s="9">
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1" s="9">
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1" s="9">
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="5" t="n"/>
+    <row r="17" s="9">
+      <c r="B17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>N/A (revisión de código del PR #11)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Backend y frontend - profesionales</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Al integrar main en la rama del PR #11 quedaron versiones antiguas de los archivos de profesionales: se perdían la búsqueda avanzada, la ficha por id, los filtros y las reseñas (FS-HU-22 a FS-HU-24), el backend no arrancaba y el build del frontend fallaba.</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 04-10-2026 al revisar el PR #11 (32 pruebas del frontend y 10 suites del backend fallaban). Luis Méndez lo corrigió en el PR #12 el 07-10-2026, que reemplazó al PR #11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" s="9">
+      <c r="B18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>CP-060 (ficha propia)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Backend - profesionales</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>En el PR #12, guardar la ficha propia solo actualizaba una fila existente de profesionales y, si no existía, lanzaba un error: todo profesional nuevo recibía "Ocurrió un error inesperado" (500) al guardar su ficha.</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 07-10-2026 al revisar el PR #12 (5 cuentas profesionales locales sin fila). Corregido el mismo día en el commit 84716a4: la ficha se crea o se actualiza (upsert; DAS, D27). Fusionado con el PR #12 el 08-10-2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" s="9">
+      <c r="B19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>CP-057 (validación de la ficha)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Backend - profesionales</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>En el PR #12, PUT /api/profesionales/mi-ficha no usaba su validador: aceptaba especialidad vacía o coordenadas fuera de rango. Además existía un POST /mi-ficha que no hacía falta.</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 07-10-2026 al revisar el PR #12 (una prueba automatizada esperaba 400 y recibía 200). Corregido en el commit 84716a4: el PUT valida la especialidad del catálogo, la comuna, la modalidad y la ubicación, y se quitó el POST.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" s="9">
+      <c r="B20" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>N/A (revisión de código del PR #12)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Configuración</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>El PR #12 eliminaba backend/.env.example y frontend/.env.example, las plantillas para configurar el proyecto en un equipo nuevo.</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Configuración</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 07-10-2026 al revisar el PR #12. Restaurados en el commit 84716a4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" s="9">
+      <c r="B21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>N/A (revisión de código del PR #12)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - perfil</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Con el PR #12 el aviso de cuenta creada o de sesión iniciada aparecía dos veces en "Mi perfil": lo mostraban el diseño común y la página.</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Interfaz</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 07-10-2026 al revisar el PR #12. Corregido en el commit 84716a4: solo lo muestra el diseño común (DisenoAplicacion).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" s="9">
+      <c r="B22" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>CP-051 (Continuar como usuario)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - Elegir perfil</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Al elegir "Usuario" en "Elegir perfil" se abría el Inicio en vez del asistente de perfil.</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 08-10-2026 por la prueba automatizada de Elegir perfil, antes de entregar el cambio. El usuario sigue con su asistente (/perfil) y el profesional va a su Inicio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" s="9">
+      <c r="B23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>CP-052 (Continuar como profesional)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - Elegir perfil</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Al elegir "Profesional", el aviso "¡Listo! Tu cuenta profesional está creada" se borraba antes de llegar al Inicio del profesional.</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 08-10-2026 por la prueba automatizada de Elegir perfil. La pantalla solo descarta el aviso que había al llegar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" s="9">
+      <c r="B24" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>CP-054 (separación por rol)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - navegación</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Con una sesión guardada antes del cambio (sin el dato rolConfirmado) y una cuenta que aún no elegía su perfil, el Inicio y "Elegir perfil" podían redirigirse entre sí sin fin.</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 08-10-2026 por la prueba automatizada del asistente. Cuando la API indica que falta elegir el perfil, se corrige la sesión guardada y la ruta protegida lleva a "Elegir perfil".</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" s="9">
+      <c r="B25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>CP-056 (revisión visual)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - menú del profesional</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>En el menú del profesional el ícono del lema se veía gigante y las etiquetas "Próximamente" se cortaban porque el menú se desbordaba.</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Interfaz</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 08-10-2026 al revisar el Inicio del profesional en el navegador. El ícono tiene tamaño fijo y en ese menú "Próximamente" se muestra como un punto naranja (el texto sigue disponible para lectores de pantalla).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" s="9">
+      <c r="B26" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>CP-050 (revisión visual)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - Elegir perfil</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>El adorno de la esquina superior tapaba parte del logo.</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Interfaz</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 08-10-2026 en el navegador. El adorno se achicó y en celular se oculta.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="9">
       <c r="B27" s="3" t="n"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
@@ -392,7 +392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1000"/>
+  <dimension ref="B1:I1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="9.380000000000001" customWidth="1" style="9" min="1" max="1"/>
@@ -1418,25 +1418,89 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1" s="9">
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1" s="9">
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="5" t="n"/>
+    <row r="27" s="9">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>CP-070 (revisión del PR #21)</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Backend - agenda</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>La validación de superposición no detectaba choques con horas en punto: CAST(parámetro AS TIME) convertía "14:00:00" en 00:00:00, así que se aceptaban bloques duplicados o superpuestos (09:00–11:00 dos veces, 10:00–12:00 encima) y se rechazaba un bloque libre (15:00–15:30).</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 12-10-2026 por Rodrigo Cárcamo al revisar el PR #21 (commit 6e850fc) contra MySQL real. Luis Méndez lo corrigió comparando TIME_TO_SEC con segundos numéricos (commit 49bf843, PR #21 fusionado el 12-10-2026). Verificado el 12-10-2026 con npm run test:mysql:agenda contra MySQL real: 39/39 (CP-070).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" s="9">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Revisión del PR #22 (límite de reservas)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Backend - reservas</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>El límite de una reserva activa por usuario con cada profesional también cuenta las reservas de horarios ya pasados. Esas reservas quedan pendientes o confirmadas para siempre y no se pueden cancelar ("El horario ya pasó"), así que el usuario queda bloqueado con ese profesional después de su primera cita.</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 12-10-2026 por Rodrigo Cárcamo al revisar el PR #22 (commits 3074e47 y 0ab6ec3) y reproducido contra MySQL real con datos temporales: 409 al reservar y 409 al intentar cancelar la cita pasada. El código aún no está en main. Corrección pedida a Luis Méndez: contar solo reservas de horarios futuros (hora de Santiago) y agregar la prueba a test:mysql:agenda.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="9">
       <c r="B29" s="3" t="n"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
@@ -1468,7 +1468,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Revisión del PR #22 (límite de reservas)</t>
+          <t>CP-079 (revisión del PR #22)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Corregido</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Detectado el 12-10-2026 por Rodrigo Cárcamo al revisar el PR #22 (commits 3074e47 y 0ab6ec3) y reproducido contra MySQL real con datos temporales: 409 al reservar y 409 al intentar cancelar la cita pasada. El código aún no está en main. Corrección pedida a Luis Méndez: contar solo reservas de horarios futuros (hora de Santiago) y agregar la prueba a test:mysql:agenda.</t>
+          <t>Detectado el 12-10-2026 por Rodrigo Cárcamo al revisar el PR #22 (commits 3074e47 y 0ab6ec3) y reproducido contra MySQL real: 409 al reservar y 409 al intentar cancelar la cita pasada. Corregido por Rodrigo Cárcamo en el mismo PR (commit 4728310): el límite cuenta solo reservas de horarios futuros (hora de Santiago) y el 409 indica su motivo. PR #22 aprobado y fusionado el 12-10-2026 (662e79c). Verificado sobre main con npm run test:mysql:agenda: 55/55 (CP-079).</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
@@ -1502,35 +1502,131 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1" s="9">
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" s="9">
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1" s="9">
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="7" t="n"/>
+    <row r="29" s="9">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>CP-077 (revisión del PR #27)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - mapa</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Si falla la descarga del estilo de OpenFreeMap, el aviso dice que el mapa «está tardando» y «Reintentar mapa» no lo recupera aunque vuelva la conexión: el reintento reutiliza el mapa ya creado y su espera del evento load, que nunca llega. Solo al recargar la página aparece el mapa.</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 15-10-2026 al revisar el PR #27 en Edge (estilo bloqueado y luego desbloqueado: 20 s después seguía sin marcadores). Corrección propuesta y probada: en el catch, eliminar el mapa si no terminó de cargar, para que el reintento cree uno nuevo. Pendiente en un PR siguiente de Nicolás Silva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" s="9">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>CP-078 (revisión del PR #27)</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - mapa</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Con teclado (Enter o Espacio sobre un marcador) se abre su ventana, pero no se cierran las demás ni se actualiza «Ver ficha de…»: la selección solo escucha el clic del mouse.</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Interfaz</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 15-10-2026 en Edge: quedaron dos ventanas abiertas y la selección en el profesional anterior. Corrección propuesta y probada: registrar la selección con ventana.on('open', …). La lista accesible bajo el mapa sigue permitiendo abrir cada ficha. Pendiente en un PR siguiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" s="9">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>CP-078 (revisión del PR #27)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - mapa</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Los controles del mapa usan los textos de MapLibre en inglés: cada marcador se anuncia como «Map marker» al lector de pantalla y los botones dicen «Zoom in», «Zoom out» y «Close popup».</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Interfaz</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 15-10-2026 en Edge. Corrección propuesta y probada: opción locale del mapa (Acercar, Alejar, Cerrar) y aria-label con el nombre y la especialidad del profesional en cada marcador. Pendiente en un PR siguiente.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="9">
       <c r="B32" s="1" t="n"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
@@ -1628,50 +1628,215 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1" s="9">
-      <c r="B32" s="1" t="n"/>
-      <c r="C32" s="1" t="n"/>
-      <c r="D32" s="1" t="n"/>
-      <c r="E32" s="1" t="n"/>
-      <c r="F32" s="1" t="n"/>
-      <c r="G32" s="1" t="n"/>
-      <c r="H32" s="1" t="n"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1" s="9">
-      <c r="B33" s="1" t="n"/>
-      <c r="C33" s="1" t="n"/>
-      <c r="D33" s="1" t="n"/>
-      <c r="E33" s="1" t="n"/>
-      <c r="F33" s="1" t="n"/>
-      <c r="G33" s="1" t="n"/>
-      <c r="H33" s="1" t="n"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1" s="9">
-      <c r="B34" s="1" t="n"/>
-      <c r="C34" s="1" t="n"/>
-      <c r="D34" s="1" t="n"/>
-      <c r="E34" s="1" t="n"/>
-      <c r="F34" s="1" t="n"/>
-      <c r="G34" s="1" t="n"/>
-      <c r="H34" s="1" t="n"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1" s="9">
-      <c r="B35" s="1" t="n"/>
-      <c r="C35" s="1" t="n"/>
-      <c r="D35" s="1" t="n"/>
-      <c r="E35" s="1" t="n"/>
-      <c r="F35" s="1" t="n"/>
-      <c r="G35" s="1" t="n"/>
-      <c r="H35" s="1" t="n"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1" s="9">
-      <c r="B36" s="1" t="n"/>
-      <c r="C36" s="1" t="n"/>
-      <c r="D36" s="1" t="n"/>
-      <c r="E36" s="1" t="n"/>
-      <c r="F36" s="1" t="n"/>
-      <c r="G36" s="1" t="n"/>
-      <c r="H36" s="1" t="n"/>
+    <row r="32" s="9">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>CP-081</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - navegación</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Al cambiar de pantalla, la página conservaba la posición de scroll de la anterior: al abrir una ficha desde abajo de la lista se entraba a mitad de página.</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Interfaz</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 13-10-2026 por Rodrigo Cárcamo al grabar el video de avance. Corregido el 19-10-2026: el componente VolverArriba (App.jsx) lleva la vista arriba en cada navegación a otra pantalla, salvo con atrás/adelante y en los cambios de filtros o de página del buscador. Verificado con CP-081.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" s="9">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>CP-082</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - agenda</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>La pregunta de confirmación (confirmar o cancelar una reserva, retirar un horario) se mostraba al final de la lista: con varias citas u horarios quedaba fuera de la pantalla y parecía que el botón no hacía nada.</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 19-10-2026 por Rodrigo Cárcamo al revisar la interfaz. Corregido el mismo día: la pregunta aparece dentro de la misma tarjeta, recibe el foco, y "Volver" o Escape la cierran y devuelven el foco al botón. Verificado con CP-082.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" s="9">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>CP-083</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - búsqueda</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Cada cambio de filtro, orden o página reemplazaba la lista por "Cargando profesionales…" y la página saltaba.</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Interfaz</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 19-10-2026 por Rodrigo Cárcamo al revisar la interfaz. Corregido el mismo día: los resultados anteriores se mantienen atenuados, con "Actualizando resultados…", hasta que llegan los nuevos. Verificado con CP-083.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" s="9">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>CP-084</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - celular</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Varios campos tenían letra menor a 16 px (0,88 a 0,95 rem en los buscadores y filtros; 13,3 px por omisión del navegador en las certificaciones y en el texto del administrador), con lo que Safari en iPhone acerca la página al tocarlos.</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Interfaz</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 19-10-2026 por Rodrigo Cárcamo al revisar la interfaz. Corregido el mismo día: los campos heredan la letra de la página (16 px). Verificado con CP-084 en Edge con emulación de celular táctil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" s="9">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>CP-082</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - agenda</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Cinco botones de la agenda usaban la clase boton--primario, que no existe en los estilos: se veían con el estilo base en vez del botón principal naranja del resto de la aplicación.</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Interfaz</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 19-10-2026 por Rodrigo Cárcamo al revisar la interfaz. Corregido el mismo día: los botones usan boton--principal. Verificado con CP-082.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="9">
       <c r="B37" s="1" t="n"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>CP-078 (revisión del PR #27)</t>
+          <t>CP-078 (revisión del PR #27); CP-096</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Corregido</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Detectado el 15-10-2026 en Edge: quedaron dos ventanas abiertas y la selección en el profesional anterior. Corrección propuesta y probada: registrar la selección con ventana.on('open', …). La lista accesible bajo el mapa sigue permitiendo abrir cada ficha. Pendiente en un PR siguiente.</t>
+          <t>Detectado el 15-10-2026 en Edge: quedaron dos ventanas abiertas y la selección en el profesional anterior. Corrección propuesta y probada: registrar la selección con ventana.on('open', …). La lista accesible bajo el mapa sigue permitiendo abrir cada ficha. Pendiente en un PR siguiente. 19-10-2026: corregido por Rodrigo Cárcamo junto con la SC-22: la selección se registra con el evento open de la ventana (con el mouse o con Enter sobre el marcador) y se cierran las demás. Verificado con CP-096 en Edge.</t>
         </is>
       </c>
     </row>
@@ -1839,13 +1839,46 @@
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="9">
-      <c r="B37" s="1" t="n"/>
-      <c r="C37" s="1" t="n"/>
-      <c r="D37" s="1" t="n"/>
-      <c r="E37" s="1" t="n"/>
-      <c r="F37" s="1" t="n"/>
-      <c r="G37" s="1" t="n"/>
-      <c r="H37" s="1" t="n"/>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>CP-094</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - mapa</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Al abrir la vista Mapa se veía de muy lejos (media Sudamérica y la Antártida): el encuadre incluía a un profesional con coordenadas fuera de Chile (la cuenta de prueba «juanito», con latitud y longitud -90) y el mapa permitía alejarse hasta ver el mundo.</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Interfaz</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Reportado el 19-10-2026 por Rodrigo Cárcamo (Product Owner). Corregido el mismo día: el mapa se limita al Chile continental (maxBounds, con un margen que incluye Juan Fernández, y sin repetir el mundo), las ubicaciones fuera de Chile no se dibujan ni se usan para encuadrar y se avisa cuáles quedan fuera (siguen en la lista). Verificado con CP-094 en Edge con el mapa real. Queda la causa de datos: la validación de la ficha acepta cualquier coordenada del mundo; limitarla a Chile corresponde a una decisión del Product Owner. El mismo 19-10-2026 el Product Owner lo decidió (SC-24): el formulario y la API solo aceptan coordenadas dentro del mismo recuadro de Chile (CP-100), así que una ficha nueva o editada ya no puede repetir el error. La ficha de «juanito» conserva -90/-90 hasta que se corrija al editarla.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="9">
       <c r="B38" s="1" t="n"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
@@ -1535,12 +1535,12 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Corregido</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Detectado el 15-10-2026 al revisar el PR #27 en Edge (estilo bloqueado y luego desbloqueado: 20 s después seguía sin marcadores). Corrección propuesta y probada: en el catch, eliminar el mapa si no terminó de cargar, para que el reintento cree uno nuevo. Pendiente en un PR siguiente de Nicolás Silva.</t>
+          <t>Detectado el 15-10-2026 al revisar el PR #27 en Edge (estilo bloqueado y luego desbloqueado: 20 s después seguía sin marcadores). Corrección propuesta y probada: en el catch, eliminar el mapa si no terminó de cargar, para que el reintento cree uno nuevo. Pendiente en un PR siguiente de Nicolás Silva. 21-10-2026: corregido por Rodrigo Cárcamo. El mapa escucha el evento error de MapLibre: si falla la descarga del estilo, avisa de inmediato «No se pudo cargar el mapa…» (antes esperaba 15 s y decía que estaba tardando) y descarta el mapa que no terminó de cargar, así «Reintentar mapa» crea uno nuevo. Una tesela que falla no lo interrumpe. Verificado con CP-101 en Edge con el estilo bloqueado y luego desbloqueado: aviso a los 0,2 s y mapa recuperado sin recargar.</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Corregido</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Detectado el 15-10-2026 en Edge. Corrección propuesta y probada: opción locale del mapa (Acercar, Alejar, Cerrar) y aria-label con el nombre y la especialidad del profesional en cada marcador. Pendiente en un PR siguiente.</t>
+          <t>Detectado el 15-10-2026 en Edge. Corrección propuesta y probada: opción locale del mapa (Acercar, Alejar, Cerrar) y aria-label con el nombre y la especialidad del profesional en cada marcador. Pendiente en un PR siguiente. 21-10-2026: corregido por Rodrigo Cárcamo con la opción locale del mapa («Acercar», «Alejar», «Cerrar ventana», «Marcador del mapa») y un aria-label con el nombre y la especialidad del profesional en cada marcador. Verificado con CP-102 en Edge.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
@@ -392,7 +392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I1000"/>
+  <dimension ref="A1:I1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="9.380000000000001" customWidth="1" style="9" min="1" max="1"/>
@@ -1881,13 +1881,46 @@
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="9">
-      <c r="B38" s="1" t="n"/>
-      <c r="C38" s="1" t="n"/>
-      <c r="D38" s="1" t="n"/>
-      <c r="E38" s="1" t="n"/>
-      <c r="F38" s="1" t="n"/>
-      <c r="G38" s="1" t="n"/>
-      <c r="H38" s="1" t="n"/>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>CP-109</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Backend - asistente IA</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Con la clave real de Groq, cada mensaje al asistente terminaba en «El asistente no está disponible en este momento»: el modelo configurado por defecto (llama-3.3-70b-versatile) ya no existe en Groq y el proveedor respondía 404 (model_not_found).</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Configuración</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 22-10-2026 por Rodrigo Cárcamo al ejecutar CP-109 con la clave real. Corregido el mismo día: el modelo por defecto pasa a openai/gpt-oss-120b (config/env.js y .env.example), elegido entre los modelos de texto activos de la cuenta (openai/gpt-oss-120b, openai/gpt-oss-20b y qwen/qwen3.8-27b) por la calidad de sus respuestas en español, en alrededor de 1 s. IA_MODELO permite cambiarlo sin tocar el código si Groq vuelve a retirar un modelo. Verificado con CP-109 (6/6).</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="9">
       <c r="B39" s="1" t="n"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
@@ -392,7 +392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:J1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="9.380000000000001" customWidth="1" style="9" min="1" max="1"/>
@@ -1923,13 +1923,46 @@
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="9">
-      <c r="B39" s="1" t="n"/>
-      <c r="C39" s="1" t="n"/>
-      <c r="D39" s="1" t="n"/>
-      <c r="E39" s="1" t="n"/>
-      <c r="F39" s="1" t="n"/>
-      <c r="G39" s="1" t="n"/>
-      <c r="H39" s="1" t="n"/>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>CP-120</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - mapa</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Al abrir Profesionales en una pestaña o ventana en segundo plano (minimizada o tapada), el mapa mostraba «El mapa está tardando en cargar. Reintenta o utiliza la lista.» aunque no había ningún problema: el navegador pausa el dibujo de las pestañas ocultas, el estilo del mapa no termina de cargar y el plazo de 15 s se cumplía igual. Con la SC-27 el mapa se ve siempre junto a la lista, así que le pasaría a cualquiera que abra la página en otra pestaña.</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 22-10-2026 por Rodrigo Cárcamo al verificar la SC-27 en Edge con la ventana minimizada. Corregido el mismo día: el plazo de carga del mapa empieza a correr cuando la pestaña se ve (evento visibilitychange); mientras está oculta se muestra «Cargando mapa…». Verificado con CP-120 en Edge (oculta: sin aviso; visible: 11 marcadores sin recargar) y con una prueba de Vitest.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="9">
       <c r="B40" s="1" t="n"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
@@ -392,7 +392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:I1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="9.380000000000001" customWidth="1" style="9" min="1" max="1"/>
@@ -1965,22 +1965,88 @@
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="9">
-      <c r="B40" s="1" t="n"/>
-      <c r="C40" s="1" t="n"/>
-      <c r="D40" s="1" t="n"/>
-      <c r="E40" s="1" t="n"/>
-      <c r="F40" s="1" t="n"/>
-      <c r="G40" s="1" t="n"/>
-      <c r="H40" s="1" t="n"/>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>CP-121</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Backend - asistente IA</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>La red de seguridad del asistente, que agrega la línea de prevención del suicidio (*4141) sin depender del modelo, no reconocía las formas más directas de expresar riesgo: «me quiero matar», «me voy a matar», «quiero morir», «tengo ganas de morir» o «quiero acabar con mi vida». En esos casos el aviso dependía solo de que el modelo lo escribiera, y el DAS dice que la respuesta siempre lo indica.</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 22-10-2026 por Claude en la revisión previa de los PR #28 a #30, antes de la revisión del equipo, y confirmado contra el patrón de proveedorIa.service.js. Corregido el mismo día por Rodrigo Cárcamo en feat/asistente-ia (PR #29): el patrón reconoce esas frases y las de «terminar con mi vida»; una prueba de Jest cubre seis frases y una de control («me muero de hambre») que no debe activarlo. Verificado con CP-121 (backend 296/296).</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="9">
-      <c r="B41" s="1" t="n"/>
-      <c r="C41" s="1" t="n"/>
-      <c r="D41" s="1" t="n"/>
-      <c r="E41" s="1" t="n"/>
-      <c r="F41" s="1" t="n"/>
-      <c r="G41" s="1" t="n"/>
-      <c r="H41" s="1" t="n"/>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>CP-122</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Backend - asistente IA</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>El límite diario del asistente (30 mensajes) se podía superar con mensajes enviados al mismo tiempo: con 29 de 30 usados, tres solicitudes simultáneas se aceptaban las tres y el contador llegaba a 32. El servicio leía el uso, esperaba la respuesta del proveedor y recién después sumaba, así que todas las solicitudes veían el mismo cupo libre.</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Informado el 23-10-2026 por Nicolás Silva en la revisión del PR #29 (cambios solicitados). Corregido el mismo día en feat/asistente-ia: el mensaje se reserva antes de llamar al proveedor con un solo UPDATE condicionado (mensajes &lt; límite) o un INSERT, y si el proveedor o el guardado fallan el cupo se devuelve. Pruebas de Jest con tres solicitudes simultáneas al iniciar y al continuar, y verificación contra MySQL real. Verificado con CP-122 (backend 304/304).</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="9">
       <c r="B42" s="1" t="n"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
@@ -392,7 +392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1000"/>
+  <dimension ref="B1:I1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="9.380000000000001" customWidth="1" style="9" min="1" max="1"/>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Informado el 23-10-2026 por Nicolás Silva en la revisión del PR #29 (cambios solicitados). Corregido el mismo día en feat/asistente-ia: el mensaje se reserva antes de llamar al proveedor con un solo UPDATE condicionado (mensajes &lt; límite) o un INSERT, y si el proveedor o el guardado fallan el cupo se devuelve. Pruebas de Jest con tres solicitudes simultáneas al iniciar y al continuar, y verificación contra MySQL real. Verificado con CP-122 (backend 304/304).</t>
+          <t>Informado el 23-10-2026 por Luis Méndez en la revisión del PR #29 (cambios solicitados). Corregido el mismo día en feat/asistente-ia: el mensaje se reserva antes de llamar al proveedor con un solo UPDATE condicionado (mensajes &lt; límite) o un INSERT, y si el proveedor o el guardado fallan el cupo se devuelve. Pruebas de Jest con tres solicitudes simultáneas al iniciar y al continuar, y verificación contra MySQL real. Verificado con CP-122 (backend 304/304). Al revisar, Luis Méndez agregó que el reinicio de día solo avance a un día posterior (una solicitud tardía del día anterior ya no reinicia el contador del día nuevo) y la comprobación npm run test:mysql:asistente (23 condiciones, todas aprobadas; Plan de Pruebas/Asistente_Cupo_MySQL*). PR #29 y #30 aprobados por Luis y fusionados en main el 23-10-2026.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
@@ -392,7 +392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I1000"/>
+  <dimension ref="A1:I1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="9.380000000000001" customWidth="1" style="9" min="1" max="1"/>
@@ -2049,22 +2049,88 @@
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="9">
-      <c r="B42" s="1" t="n"/>
-      <c r="C42" s="1" t="n"/>
-      <c r="D42" s="1" t="n"/>
-      <c r="E42" s="1" t="n"/>
-      <c r="F42" s="1" t="n"/>
-      <c r="G42" s="1" t="n"/>
-      <c r="H42" s="1" t="n"/>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>CP-128</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - portada</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>En la portada rediseñada (PR #33), los tiradores dorados de las puertas de la escena cruzaban el texto de bienvenida: en celular atravesaban el título «a tu ritmo.» y el párrafo, y a 1024 px el tirador izquierdo cruzaba el final del párrafo. Es lo primero que lee un visitante.</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Interfaz</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 26-10-2026 por Claude en la revisión del PR #33 (de Luis Méndez) pedida a Rodrigo Cárcamo, que aprobó el PR y pidió hacer los ajustes aparte. Corregido el mismo día en la rama fix/portada-inicio-ajustes: bajo 800 px, donde el texto usa todo el ancho, los tiradores se ocultan (quedan las puertas y su unión); desde 800 px el texto de bienvenida se limita a la puerta izquierda y el título llega a 5,2 rem como máximo, en dos líneas. Medido a 375, 700, 800, 1024, 1440 y 1920 px: ninguna línea de texto cruza un tirador y no hay desborde horizontal. Verificado con CP-128.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="9">
-      <c r="B43" s="1" t="n"/>
-      <c r="C43" s="1" t="n"/>
-      <c r="D43" s="1" t="n"/>
-      <c r="E43" s="1" t="n"/>
-      <c r="F43" s="1" t="n"/>
-      <c r="G43" s="1" t="n"/>
-      <c r="H43" s="1" t="n"/>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>CP-129</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - portada (accesibilidad)</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Al avanzar la escena de la portada, el único h1 («Tu bienestar, a tu ritmo.») y el aviso de cierre de sesión quedaban dentro del primer paso, que se vuelve aria-hidden e inert: quien usa lector de pantalla y ya bajó por la página perdía el título principal y el aviso.</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 26-10-2026 por Claude en la misma revisión del PR #33. Corregido en fix/portada-inicio-ajustes: el h1 (para lector de pantalla) y el aviso quedan fuera de los pasos que se inactivan; el título visible del primer paso se oculta al lector para no leerse dos veces. Prueba de Vitest nueva (falla con el componente anterior y pasa con el corregido); frontend 286/286. Verificado con CP-129.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="9">
       <c r="B44" s="1" t="n"/>
